--- a/forms/trg/Formulir_TRG_marg.xlsx
+++ b/forms/trg/Formulir_TRG_marg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B37)</f>
+        <f>COUNTA(Anggota!B5:B38)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F37)</f>
+        <f>COUNTA(Anggota!F5:F38)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Hardiyanti Munsi, S.Sos.,M.Si</t>
+          <t>Prof. Dr. Munsi Lampe, MA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Antropologi dan Budaya Organisasi</t>
+          <t>Anthropology Maritim; Anthropology Marine; Ethnicity; Culture</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,11 +933,19 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-5425-2707</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+          <t>0000-0002-9922-4017</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6023376</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57212148002</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,22 +958,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Eymal B Demmalino, M.Si</t>
+          <t>Hardiyanti Munsi, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Agribusiness Study Program, Faculty of Agriculture, Hasanuddin University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Maritime‬; ‪Agriculture‬; ‪Environmental Science‬.</t>
+          <t>Antropologi dan Budaya Organisasi</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -978,19 +982,11 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2316-5951</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6088441</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57217217078</t>
-        </is>
-      </c>
+          <t>0009-0006-5425-2707</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1003,22 +999,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Pawennari Hijjang, MA</t>
+          <t>Prof. Dr. Eymal B Demmalino, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
+          <t>Agribusiness Study Program, Faculty of Agriculture, Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Anthropology; Ecology; Culture; Local Community.</t>
+          <t>Maritime‬; ‪Agriculture‬; ‪Environmental Science‬.</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,17 +1023,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-6560-9639</t>
+          <t>0000-0003-2316-5951</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6023371</t>
+          <t>6088441</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57212144511</t>
+          <t>57217217078</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1052,12 +1048,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Neil, S.Sos.,M.Si</t>
+          <t>Prof. Dr. Pawennari Hijjang, MA</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1067,18 +1063,26 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Anthropology Marine; Coastal Communities; Maritim Culture</t>
+          <t>Anthropology; Ecology; Culture; Local Community.</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-6560-9639</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6023371</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>36344705400</t>
+          <t>57212144511</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,12 +1097,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ahmad Ismail, S.Sos.,M.Si</t>
+          <t>Muhammad Neil, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1108,26 +1112,18 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Anthropology; Media; Local Community; Identity.</t>
+          <t>Anthropology Marine; Coastal Communities; Maritim Culture</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2949-7802</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>6665334</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57212142711</t>
+          <t>36344705400</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1142,22 +1138,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Hardiyanti Munsi, S.Sos.,M.Si</t>
+          <t>Dr. Ahmad Ismail, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Antropologi dan Budaya Organisasi</t>
+          <t>Anthropology; Media; Local Community; Identity.</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1166,11 +1162,19 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-5425-2707</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+          <t>0000-0002-2949-7802</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>6665334</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57212142711</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1183,22 +1187,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Eymal B Demmalino, M.Si</t>
+          <t>Hardiyanti Munsi, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Agribusiness Study Program, Faculty of Agriculture, Hasanuddin University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Maritime‬; ‪Agriculture‬; ‪Environmental Science‬.</t>
+          <t>Antropologi dan Budaya Organisasi</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1207,19 +1211,11 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2316-5951</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>6088441</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>57217217078</t>
-        </is>
-      </c>
+          <t>0009-0006-5425-2707</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1232,22 +1228,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Pawennari Hijjang, MA</t>
+          <t>Prof. Dr. Eymal B Demmalino, M.Si</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
+          <t>Agribusiness Study Program, Faculty of Agriculture, Hasanuddin University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Anthropology; Ecology; Culture; Local Community.</t>
+          <t>Maritime‬; ‪Agriculture‬; ‪Environmental Science‬.</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1256,17 +1252,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-6560-9639</t>
+          <t>0000-0003-2316-5951</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>6023371</t>
+          <t>6088441</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57212144511</t>
+          <t>57217217078</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1281,12 +1277,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Neil, S.Sos.,M.Si</t>
+          <t>Prof. Dr. Pawennari Hijjang, MA</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1296,18 +1292,26 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Anthropology Marine; Coastal Communities; Maritim Culture</t>
+          <t>Anthropology; Ecology; Culture; Local Community.</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-6560-9639</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>6023371</t>
+        </is>
+      </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>36344705400</t>
+          <t>57212144511</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1322,12 +1326,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ahmad Ismail, S.Sos.,M.Si</t>
+          <t>Muhammad Neil, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1337,26 +1341,18 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Anthropology; Media; Local Community; Identity.</t>
+          <t>Anthropology Marine; Coastal Communities; Maritim Culture</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2949-7802</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>6665334</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>57212142711</t>
+          <t>36344705400</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1371,31 +1367,43 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>moizes dos Reis Borromeu, S.P.,M.P.</t>
+          <t>Dr. Ahmad Ismail, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>East Timor Coffee Institute (ETCI)</t>
+          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ecology; Agribisnis</t>
+          <t>Anthropology; Media; Local Community; Identity.</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2949-7802</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>6665334</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>57212142711</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1408,43 +1416,31 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Dr. Fitrawan Umar, S.T., M.Sc.</t>
+          <t>moizes dos Reis Borromeu, S.P.,M.P.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency (BRIN)</t>
+          <t>East Timor Coffee Institute (ETCI)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Urban and Regional Planning; Rural Studies; Human Ecology</t>
+          <t>Ecology; Agribisnis</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-1710-7512</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>6644121</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>58767356800</t>
-        </is>
-      </c>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1457,31 +1453,43 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Abdul Masli, S.Sos, MA</t>
+          <t>Dr. Fitrawan Umar, S.T., M.Sc.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Yayasan Antropos Indonesia; MARG</t>
+          <t>National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Anthropology; Empowerment; Community</t>
+          <t>Urban and Regional Planning; Rural Studies; Human Ecology</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-1710-7512</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>6644121</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>58767356800</t>
+        </is>
+      </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1494,39 +1502,31 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Andi Batara Al Isra, S.Sos.,M.A</t>
+          <t>Abdul Masli, S.Sos, MA</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
+          <t>Yayasan Antropos Indonesia; MARG</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Anthropology;</t>
+          <t>Anthropology; Empowerment; Community</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>0009-0004-3591-204X</t>
-        </is>
-      </c>
+      <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>58781609500</t>
-        </is>
-      </c>
+      <c r="L18" s="12" t="n"/>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1539,31 +1539,39 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Utari Nur Pratiwi, S.Sos</t>
+          <t>Andi Batara Al Isra, S.Sos.,M.A</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Yayasan Antropos Indonesia</t>
+          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Anthropologi Maritim</t>
+          <t>Anthropology;</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>0009-0004-3591-204X</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>58781609500</t>
+        </is>
+      </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1576,20 +1584,24 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Halisa Salsabila T</t>
+          <t>Utari Nur Pratiwi, S.Sos</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="n"/>
+          <t>Yayasan Antropos Indonesia</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Anthropologi Maritim</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1609,12 +1621,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>M. Irwan Eka Kumalajaya</t>
+          <t>Halisa Salsabila T</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1622,11 +1634,7 @@
           <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Anthropology</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
@@ -1646,22 +1654,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Muzakkir, S.Sos</t>
+          <t>M. Irwan Eka Kumalajaya</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Coral Triangle Center</t>
+          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Community Development</t>
+          <t>Anthropology</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1683,22 +1691,22 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Shakila Maharani Ikhsan</t>
+          <t>Ahmad Muzakkir, S.Sos</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
+          <t>Coral Triangle Center</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Anthropology</t>
+          <t>Community Development</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1720,12 +1728,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Zalsabilah Mustafa</t>
+          <t>Shakila Maharani Ikhsan</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1757,12 +1765,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Andi Amelia Putri Indra</t>
+          <t>Zalsabilah Mustafa</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1792,10 +1800,26 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="11" t="n"/>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Andi Amelia Putri Indra</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Department of Anthropology, Faculty of Social and Political Sciences, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Anthropology</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
@@ -1803,7 +1827,11 @@
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="12" t="n"/>
       <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1992,15 +2020,32 @@
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="12" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
